--- a/data/research-experience_en.xlsx
+++ b/data/research-experience_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A31F3F3-6386-4EA4-A2B9-24160033D8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C618FA-8BF3-408A-9FAA-86513E01690D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28020" yWindow="780" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research experience" sheetId="1" r:id="rId1"/>
@@ -103,9 +103,6 @@
     <t>Oct. 2023 - Present</t>
   </si>
   <si>
-    <t>Dec. 2023 - Present</t>
-  </si>
-  <si>
     <t>Jan. 2013 - Jun. 2015</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
   </si>
   <si>
     <t>Neurognosis research incubator leader (2013-2014)</t>
+  </si>
+  <si>
+    <t>Dec. 2023 - Dec. 2024</t>
   </si>
 </sst>
 </file>
@@ -449,16 +449,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="70" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="70" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="128.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="128.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="121.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="121.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -475,7 +475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -492,22 +492,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -519,7 +519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -536,12 +536,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -550,7 +550,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -567,12 +567,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>22</v>
@@ -581,86 +581,86 @@
         <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
